--- a/demo/mc_v12/fixtures/F05_课题二_常数列_仅告警.xlsx
+++ b/demo/mc_v12/fixtures/F05_课题二_常数列_仅告警.xlsx
@@ -547,7 +547,7 @@
       <c r="B2" s="3" t="inlineStr"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>必填, 与系统中场地编号一致</t>
+          <t>可留空(以页面所选场地为准); 填写时须与系统中场地编号一致</t>
         </is>
       </c>
     </row>
